--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:58:27+00:00</t>
+    <t>2026-01-23T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T10:30:04+00:00</t>
+    <t>2026-01-27T15:50:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:50:42+00:00</t>
+    <t>2026-01-28T14:07:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:07:57+00:00</t>
+    <t>2026-01-29T08:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:29:40+00:00</t>
+    <t>2026-01-30T16:24:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T16:24:47+00:00</t>
+    <t>2026-02-02T09:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:56:46+00:00</t>
+    <t>2026-02-04T09:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:47:16+00:00</t>
+    <t>2026-02-04T14:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:08:59+00:00</t>
+    <t>2026-02-04T16:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
